--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,353 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122649539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56692</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Erstaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>685401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6574006</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122649524</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>685336</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6574043</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122649591</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57389</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>685230</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6574032</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649539</v>
+        <v>122649524</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>57479</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685401</v>
+        <v>685336</v>
       </c>
       <c r="R5" t="n">
-        <v>6574006</v>
+        <v>6574043</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,6 +1128,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649524</v>
+        <v>122649591</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,7 +1201,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1206,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685336</v>
+        <v>685230</v>
       </c>
       <c r="R6" t="n">
-        <v>6574043</v>
+        <v>6574032</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,17 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649591</v>
+        <v>122649539</v>
       </c>
       <c r="B7" t="n">
-        <v>57389</v>
+        <v>56693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685230</v>
+        <v>685401</v>
       </c>
       <c r="R7" t="n">
-        <v>6574032</v>
+        <v>6574006</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649591</v>
+        <v>122649539</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>56693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,14 +1207,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685230</v>
+        <v>685401</v>
       </c>
       <c r="R6" t="n">
-        <v>6574032</v>
+        <v>6574006</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B7" t="n">
-        <v>56693</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R7" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B5" t="n">
-        <v>57479</v>
+        <v>56693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R5" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,11 +1128,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649539</v>
+        <v>122649524</v>
       </c>
       <c r="B6" t="n">
-        <v>56693</v>
+        <v>57479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1201,23 +1196,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685401</v>
+        <v>685336</v>
       </c>
       <c r="R6" t="n">
-        <v>6574006</v>
+        <v>6574043</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,6 +1242,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649539</v>
+        <v>122649524</v>
       </c>
       <c r="B5" t="n">
-        <v>56693</v>
+        <v>57479</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685401</v>
+        <v>685336</v>
       </c>
       <c r="R5" t="n">
-        <v>6574006</v>
+        <v>6574043</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,6 +1128,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B6" t="n">
-        <v>57479</v>
+        <v>56693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,16 +1179,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1196,23 +1201,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R6" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,11 +1247,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B5" t="n">
-        <v>57479</v>
+        <v>56787</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R5" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,11 +1128,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649539</v>
+        <v>122649524</v>
       </c>
       <c r="B6" t="n">
-        <v>56693</v>
+        <v>57573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1201,23 +1196,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685401</v>
+        <v>685336</v>
       </c>
       <c r="R6" t="n">
-        <v>6574006</v>
+        <v>6574043</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,6 +1242,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
         <v>122649591</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>57484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B5" t="n">
-        <v>56787</v>
+        <v>57484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1088,14 +1088,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R5" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B6" t="n">
-        <v>57573</v>
+        <v>56787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1196,23 +1196,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R6" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,11 +1242,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649591</v>
+        <v>122649524</v>
       </c>
       <c r="B7" t="n">
-        <v>57484</v>
+        <v>57573</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1284,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,7 +1310,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1325,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685230</v>
+        <v>685336</v>
       </c>
       <c r="R7" t="n">
-        <v>6574032</v>
+        <v>6574043</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,12 +1350,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649591</v>
+        <v>122649524</v>
       </c>
       <c r="B5" t="n">
-        <v>57484</v>
+        <v>57573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685230</v>
+        <v>685336</v>
       </c>
       <c r="R5" t="n">
-        <v>6574032</v>
+        <v>6574043</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,12 +1122,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B6" t="n">
-        <v>56787</v>
+        <v>57484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1202,14 +1207,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R6" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,12 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B7" t="n">
-        <v>57573</v>
+        <v>56787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,16 +1293,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,23 +1315,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R7" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,11 +1361,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649591</v>
+        <v>122649539</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
+        <v>56787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,14 +1207,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685230</v>
+        <v>685401</v>
       </c>
       <c r="R6" t="n">
-        <v>6574032</v>
+        <v>6574006</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B7" t="n">
-        <v>56787</v>
+        <v>57484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R7" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B6" t="n">
-        <v>56787</v>
+        <v>57484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,14 +1207,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R6" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649591</v>
+        <v>122649539</v>
       </c>
       <c r="B7" t="n">
-        <v>57484</v>
+        <v>56787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685230</v>
+        <v>685401</v>
       </c>
       <c r="R7" t="n">
-        <v>6574032</v>
+        <v>6574006</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B5" t="n">
-        <v>57573</v>
+        <v>56787</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R5" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,11 +1128,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649591</v>
+        <v>122649524</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
+        <v>57573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1170,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,7 +1196,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1211,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685230</v>
+        <v>685336</v>
       </c>
       <c r="R6" t="n">
-        <v>6574032</v>
+        <v>6574043</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,12 +1236,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649539</v>
+        <v>122649591</v>
       </c>
       <c r="B7" t="n">
-        <v>56787</v>
+        <v>57484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685401</v>
+        <v>685230</v>
       </c>
       <c r="R7" t="n">
-        <v>6574006</v>
+        <v>6574032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649524</v>
+        <v>122649591</v>
       </c>
       <c r="B6" t="n">
-        <v>57573</v>
+        <v>57484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,25 +1170,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,7 +1196,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685336</v>
+        <v>685230</v>
       </c>
       <c r="R6" t="n">
-        <v>6574043</v>
+        <v>6574032</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,17 +1236,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649591</v>
+        <v>122649524</v>
       </c>
       <c r="B7" t="n">
-        <v>57484</v>
+        <v>57573</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1284,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,7 +1310,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1325,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685230</v>
+        <v>685336</v>
       </c>
       <c r="R7" t="n">
-        <v>6574032</v>
+        <v>6574043</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,12 +1350,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45510-2020 artfynd.xlsx
+++ b/artfynd/A 45510-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649539</v>
+        <v>122649524</v>
       </c>
       <c r="B5" t="n">
-        <v>56787</v>
+        <v>57573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,23 +1082,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erstaviken, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685401</v>
+        <v>685336</v>
       </c>
       <c r="R5" t="n">
-        <v>6574006</v>
+        <v>6574043</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,6 +1128,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649524</v>
+        <v>122649539</v>
       </c>
       <c r="B7" t="n">
-        <v>57573</v>
+        <v>56787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,16 +1293,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,23 +1315,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Erstaviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685336</v>
+        <v>685401</v>
       </c>
       <c r="R7" t="n">
-        <v>6574043</v>
+        <v>6574006</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,11 +1361,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Varnande par vid bo med minst en unge.</t>
         </is>
       </c>
       <c r="AD7" t="b">
